--- a/input_courses/科研训练计划_2024-2025-2/02_学生成绩表_生成核查报告.xlsx
+++ b/input_courses/科研训练计划_2024-2025-2/02_学生成绩表_生成核查报告.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,89 +446,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>学生人数</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>80</v>
+          <t>原始成绩表文件名</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-2025-2 科研训练计划.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>是否存在缺失学号</t>
+          <t>课程名称</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>科研训练计划</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>是否存在重复学号</t>
+          <t>课程类型</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>非试卷型</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>学号是否按字符串读取</t>
+          <t>成绩拆分模式</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>按权重拆分</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>课程目标编号是否统一</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
+          <t>学生人数</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>每个课程目标人数是否一致</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
+          <t>课程目标数量</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>是否存在空成绩</t>
+          <t>每个课程目标对应的学生记录数</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>课程目标1：80条；课程目标2：80条；课程目标3：80条</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>是否存在超出满分的成绩</t>
+          <t>是否存在缺失学号</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -540,22 +538,142 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>原始总评成绩与转换后复核总评成绩的误差</t>
+          <t>是否存在重复学号</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>最大绝对误差 0.000000，平均绝对误差 0.000000</t>
+          <t>否（长表中同一学生对应多个课程目标属于正常）</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>学号是否按字符串读取</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>课程目标编号是否统一</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>每个课程目标人数是否一致</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>是否存在缺失成绩</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>是否存在超出合理范围的成绩</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>原始总评成绩与转换后复核总评成绩的最大误差</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>原始总评成绩与转换后复核总评成绩的平均误差</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0.000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>原始总评成绩与转换后复核总评成绩的误差</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>最大绝对误差 0.000000，平均绝对误差 0.000000</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>是否通过核查</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>风险提示</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>该 02 表由原始总评成绩按课程目标权重拆分生成，适合历史数据补录、流程测试和无分项成绩条件下的达成度估算；若用于正式归档，建议结合课程原始评分记录进行人工复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>数据来源说明</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>按课程目标权重拆分</t>
         </is>
@@ -572,7 +690,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -583,7 +701,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>人数</t>
+          <t>学生记录数</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>学生人数</t>
         </is>
       </c>
     </row>
@@ -596,6 +719,9 @@
       <c r="B2" t="n">
         <v>80</v>
       </c>
+      <c r="C2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -606,6 +732,9 @@
       <c r="B3" t="n">
         <v>80</v>
       </c>
+      <c r="C3" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -614,6 +743,9 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>80</v>
+      </c>
+      <c r="C4" t="n">
         <v>80</v>
       </c>
     </row>
